--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_att_conversion.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_att_conversion.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_att_conversion" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_att_conversion!$B$1:$B$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_att_conversion!$A$4:$M$131</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="102">
   <si>
     <t>ID</t>
   </si>
@@ -75,10 +75,40 @@
     <t>属性中文名称及备注</t>
   </si>
   <si>
-    <t>1点力量转换的属性（万分比）</t>
-  </si>
-  <si>
-    <t>1点敏捷转换的属性（万分比）</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点力量转换的属性（万分比）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点敏捷转换的属性（万分比）</t>
+    </r>
   </si>
   <si>
     <t>1点智力转换的属性（万分比）</t>
@@ -90,9 +120,88 @@
     <t>1点统帅转换的属性（万分比）</t>
   </si>
   <si>
-    <t>1点其他属性转化的属性（万分比）
-其他属性填写att_info中ID
-格式：属性ID#转化比</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点其他属性转化的属性（万分比）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其他属性填写</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>att_info</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">ID
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>格式：属性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ID#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>转化比</t>
+    </r>
   </si>
   <si>
     <t>默认职业归属
@@ -342,9 +451,6 @@
   </si>
   <si>
     <t>7#1|7#2|7#3|7#4</t>
-  </si>
-  <si>
-    <t>301011#5000</t>
   </si>
 </sst>
 </file>
@@ -357,7 +463,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -517,13 +623,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -986,17 +1085,23 @@
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1564,8 +1669,8 @@
     <col min="6" max="6" width="15.4285714285714" style="2" customWidth="1"/>
     <col min="7" max="8" width="9" style="2" customWidth="1"/>
     <col min="9" max="9" width="34.7142857142857" style="2" customWidth="1"/>
-    <col min="10" max="10" width="43" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9.71428571428571" style="2" customWidth="1"/>
+    <col min="10" max="10" width="29" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18.4285714285714" style="2" customWidth="1"/>
     <col min="12" max="12" width="9" style="2" customWidth="1"/>
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
@@ -1615,10 +1720,10 @@
       <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -1630,17 +1735,17 @@
       <c r="H2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" ht="18" customHeight="1" spans="1:11">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -1717,7 +1822,7 @@
       <c r="B5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>38</v>
       </c>
       <c r="D5" s="2">
@@ -1737,7 +1842,7 @@
       <c r="B6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="2">
@@ -1757,7 +1862,7 @@
       <c r="B7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="2">
@@ -1804,7 +1909,7 @@
         <v>47</v>
       </c>
       <c r="E9" s="2">
-        <v>3334</v>
+        <v>3000</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>39</v>
@@ -1820,11 +1925,11 @@
       <c r="B10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>49</v>
       </c>
       <c r="E10" s="2">
-        <v>3334</v>
+        <v>3000</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>39</v>
@@ -1864,7 +1969,7 @@
         <v>53</v>
       </c>
       <c r="E12" s="2">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>39</v>
@@ -1884,7 +1989,7 @@
         <v>55</v>
       </c>
       <c r="G13" s="2">
-        <v>100000</v>
+        <v>30000</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>39</v>
@@ -1920,7 +2025,7 @@
       <c r="B15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>59</v>
       </c>
       <c r="F15" s="2">
@@ -1940,7 +2045,7 @@
       <c r="B16" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="1">
@@ -1953,7 +2058,7 @@
         <v>12000</v>
       </c>
       <c r="G16" s="1">
-        <v>12000</v>
+        <v>120000</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
@@ -1973,7 +2078,7 @@
       <c r="B17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D17" s="2">
@@ -1983,7 +2088,7 @@
         <v>2000</v>
       </c>
       <c r="F17" s="2">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="G17" s="2">
         <v>3000</v>
@@ -2002,10 +2107,10 @@
       <c r="B18" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="6">
         <v>1.25</v>
       </c>
       <c r="J18" s="2" t="s">
@@ -2022,12 +2127,12 @@
       <c r="B19" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="6"/>
       <c r="G19" s="2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>39</v>
@@ -2043,7 +2148,7 @@
       <c r="B20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>70</v>
       </c>
       <c r="F20" s="2">
@@ -2063,10 +2168,10 @@
       <c r="B21" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="6"/>
       <c r="F21" s="2">
         <v>10</v>
       </c>
@@ -2084,11 +2189,11 @@
       <c r="B22" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>74</v>
       </c>
       <c r="F22" s="2">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>39</v>
@@ -2104,8 +2209,11 @@
       <c r="B23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>38</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1250</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>75</v>
@@ -2121,8 +2229,11 @@
       <c r="B24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>41</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2500</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>75</v>
@@ -2205,7 +2316,7 @@
         <v>49</v>
       </c>
       <c r="E28" s="2">
-        <v>3334</v>
+        <v>3000</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>75</v>
@@ -2241,7 +2352,7 @@
       <c r="B30" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>77</v>
       </c>
       <c r="E30" s="2">
@@ -2265,7 +2376,7 @@
         <v>55</v>
       </c>
       <c r="G31" s="2">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>75</v>
@@ -2285,7 +2396,7 @@
         <v>57</v>
       </c>
       <c r="F32" s="2">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>75</v>
@@ -2398,7 +2509,7 @@
         <v>2000</v>
       </c>
       <c r="E37" s="2">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="F37" s="2">
         <v>2000</v>
@@ -2420,12 +2531,12 @@
       <c r="B38" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="4"/>
+      <c r="D38" s="6"/>
       <c r="G38" s="2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>75</v>
@@ -2441,7 +2552,7 @@
       <c r="B39" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="6" t="s">
         <v>70</v>
       </c>
       <c r="J39" s="2" t="s">
@@ -2458,11 +2569,11 @@
       <c r="B40" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="6" t="s">
         <v>74</v>
       </c>
       <c r="G40" s="2">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>75</v>
@@ -2478,14 +2589,14 @@
       <c r="B41" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="6" t="s">
         <v>38</v>
       </c>
       <c r="D41" s="2">
-        <v>714</v>
+        <v>1250</v>
       </c>
       <c r="E41" s="2">
-        <v>1429</v>
+        <v>1250</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>84</v>
@@ -2501,11 +2612,11 @@
       <c r="B42" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="6" t="s">
         <v>41</v>
       </c>
       <c r="D42" s="2">
-        <v>1250</v>
+        <v>2500</v>
       </c>
       <c r="E42" s="2">
         <v>2500</v>
@@ -2531,7 +2642,7 @@
         <v>2500</v>
       </c>
       <c r="E43" s="2">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>84</v>
@@ -2651,7 +2762,7 @@
         <v>55</v>
       </c>
       <c r="G49" s="2">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>84</v>
@@ -2687,7 +2798,7 @@
       <c r="B51" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D51" s="1">
@@ -2783,10 +2894,10 @@
       <c r="B55" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D55" s="4"/>
+      <c r="D55" s="6"/>
       <c r="G55" s="2">
         <v>1000</v>
       </c>
@@ -2804,7 +2915,7 @@
       <c r="B56" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="6" t="s">
         <v>70</v>
       </c>
       <c r="J56" s="2" t="s">
@@ -2821,11 +2932,11 @@
       <c r="B57" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="6" t="s">
         <v>74</v>
       </c>
       <c r="G57" s="2">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>84</v>
@@ -2845,10 +2956,10 @@
         <v>85</v>
       </c>
       <c r="D58" s="1">
-        <v>1667</v>
+        <v>1500</v>
       </c>
       <c r="F58" s="1">
-        <v>844</v>
+        <v>800</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>86</v>
@@ -2994,7 +3105,7 @@
         <v>53</v>
       </c>
       <c r="E65" s="1">
-        <v>667</v>
+        <v>1000</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>86</v>
@@ -3034,7 +3145,7 @@
         <v>79</v>
       </c>
       <c r="F67" s="1">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>86</v>
@@ -3212,7 +3323,7 @@
         <v>74</v>
       </c>
       <c r="G75" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>86</v>
@@ -3232,10 +3343,10 @@
         <v>85</v>
       </c>
       <c r="D76" s="1">
-        <v>1429</v>
+        <v>1500</v>
       </c>
       <c r="F76" s="1">
-        <v>714</v>
+        <v>800</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>88</v>
@@ -3258,10 +3369,7 @@
         <v>2500</v>
       </c>
       <c r="F77" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H77" s="1">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>88</v>
@@ -3284,10 +3392,7 @@
         <v>2500</v>
       </c>
       <c r="E78" s="1">
-        <v>6667</v>
-      </c>
-      <c r="H78" s="1">
-        <v>6667</v>
+        <v>15000</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>88</v>
@@ -3307,7 +3412,7 @@
         <v>45</v>
       </c>
       <c r="E79" s="1">
-        <v>40000</v>
+        <v>35000</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>88</v>
@@ -3327,7 +3432,7 @@
         <v>47</v>
       </c>
       <c r="E80" s="1">
-        <v>1429</v>
+        <v>2500</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>88</v>
@@ -3347,7 +3452,7 @@
         <v>49</v>
       </c>
       <c r="E81" s="1">
-        <v>1429</v>
+        <v>3000</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>88</v>
@@ -3367,7 +3472,7 @@
         <v>51</v>
       </c>
       <c r="E82" s="1">
-        <v>5000</v>
+        <v>1250</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>88</v>
@@ -3427,7 +3532,7 @@
         <v>57</v>
       </c>
       <c r="F85" s="1">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>88</v>
@@ -3494,7 +3599,7 @@
       <c r="B89" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C89" s="7" t="s">
         <v>61</v>
       </c>
       <c r="D89" s="1">
@@ -3541,6 +3646,9 @@
       <c r="G90" s="1">
         <v>1000</v>
       </c>
+      <c r="H90" s="1">
+        <v>3000</v>
+      </c>
       <c r="J90" s="1" t="s">
         <v>88</v>
       </c>
@@ -3555,7 +3663,7 @@
       <c r="B91" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="C91" s="7" t="s">
         <v>77</v>
       </c>
       <c r="J91" s="1" t="s">
@@ -3613,7 +3721,7 @@
         <v>74</v>
       </c>
       <c r="G94" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>88</v>
@@ -3633,7 +3741,7 @@
         <v>85</v>
       </c>
       <c r="D95" s="1">
-        <v>1429</v>
+        <v>1400</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>95</v>
@@ -3696,7 +3804,7 @@
         <v>47</v>
       </c>
       <c r="E98" s="1">
-        <v>3334</v>
+        <v>3000</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>95</v>
@@ -3793,7 +3901,7 @@
         <v>79</v>
       </c>
       <c r="F103" s="1">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="J103" s="1" t="s">
         <v>95</v>
@@ -3833,7 +3941,7 @@
         <v>98</v>
       </c>
       <c r="F105" s="1">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="J105" s="1" t="s">
         <v>95</v>
@@ -3908,13 +4016,13 @@
         <v>2000</v>
       </c>
       <c r="E108" s="1">
-        <v>3334</v>
+        <v>3000</v>
       </c>
       <c r="F108" s="1">
         <v>1500</v>
       </c>
       <c r="G108" s="1">
-        <v>3334</v>
+        <v>3000</v>
       </c>
       <c r="J108" s="1" t="s">
         <v>95</v>
@@ -3991,7 +4099,7 @@
         <v>74</v>
       </c>
       <c r="G112" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="J112" s="1" t="s">
         <v>95</v>
@@ -4007,7 +4115,7 @@
       <c r="B113" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="6" t="s">
         <v>38</v>
       </c>
       <c r="D113" s="1">
@@ -4027,7 +4135,7 @@
       <c r="B114" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="6" t="s">
         <v>41</v>
       </c>
       <c r="D114" s="1">
@@ -4096,9 +4204,7 @@
       <c r="E117" s="2">
         <v>3334</v>
       </c>
-      <c r="I117" s="2" t="s">
-        <v>102</v>
-      </c>
+      <c r="I117" s="1"/>
       <c r="J117" s="2" t="s">
         <v>101</v>
       </c>
@@ -4153,7 +4259,7 @@
       <c r="B120" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="6" t="s">
         <v>77</v>
       </c>
       <c r="E120" s="2">
@@ -4237,7 +4343,7 @@
         <v>81</v>
       </c>
       <c r="F124" s="2">
-        <v>3334</v>
+        <v>3300</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>101</v>
@@ -4313,10 +4419,10 @@
         <v>4000</v>
       </c>
       <c r="F127" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G127" s="2">
         <v>2000</v>
-      </c>
-      <c r="G127" s="2">
-        <v>3334</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>101</v>
@@ -4332,10 +4438,10 @@
       <c r="B128" t="s">
         <v>67</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D128" s="4"/>
+      <c r="D128" s="6"/>
       <c r="G128" s="2">
         <v>1000</v>
       </c>
@@ -4353,7 +4459,7 @@
       <c r="B129" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" s="6" t="s">
         <v>70</v>
       </c>
       <c r="J129" s="2" t="s">
@@ -4370,11 +4476,11 @@
       <c r="B130" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" s="6" t="s">
         <v>74</v>
       </c>
       <c r="G130" s="2">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>101</v>
@@ -4390,13 +4496,13 @@
       <c r="B131" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C131" s="6" t="s">
         <v>59</v>
       </c>
       <c r="F131" s="2">
         <v>2</v>
       </c>
-      <c r="J131" s="6" t="s">
+      <c r="J131" s="8" t="s">
         <v>101</v>
       </c>
       <c r="K131" s="2">
@@ -4404,7 +4510,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B131" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:M131" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B18">

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_att_conversion.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_att_conversion.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_att_conversion" sheetId="1" r:id="rId1"/>
@@ -1969,7 +1974,7 @@
         <v>53</v>
       </c>
       <c r="E12" s="2">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>39</v>
@@ -3666,6 +3671,9 @@
       <c r="C91" s="7" t="s">
         <v>77</v>
       </c>
+      <c r="E91" s="2">
+        <v>1000</v>
+      </c>
       <c r="J91" s="1" t="s">
         <v>88</v>
       </c>
@@ -3843,6 +3851,9 @@
       <c r="C100" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="E100" s="2">
+        <v>1000</v>
+      </c>
       <c r="J100" s="1" t="s">
         <v>95</v>
       </c>
@@ -4042,7 +4053,7 @@
         <v>77</v>
       </c>
       <c r="E109" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>95</v>
